--- a/inquiry_forms/031_custom_tailoring_inquiry_contact_form--inquiry_forms.xlsx
+++ b/inquiry_forms/031_custom_tailoring_inquiry_contact_form--inquiry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>custom_tailoring_inquiry_contact_form_page_1</t>
+          <t>custom_tailoring_inquiry_contact_form_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>select_tailoring_service_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Customer Name</t>
+          <t>What is the type of tailoring service?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>customer_email</t>
+          <t>select_service_location</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Customer Email</t>
+          <t>Which location do you want to receive service at?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>customer_phone</t>
+          <t>select_service_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Customer Phone</t>
+          <t>What is the preferred service time?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>customer_address</t>
+          <t>select_service_frequency</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Customer Address</t>
+          <t>How often would you like to get service?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>customer_inquiry</t>
+          <t>select_service_day</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inquiry Description</t>
+          <t>Which day of the week?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>customer_message</t>
+          <t>select_service_time_frame</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Message</t>
+          <t>Time Frame</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>select_inquiry_type</t>
+          <t>customer_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the type of tailoring service?</t>
+          <t>Customer Name</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>select_service_location</t>
+          <t>customer_email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Which location do you want to receive service at?</t>
+          <t>Customer Email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>select_service_time</t>
+          <t>customer_phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is the preferred service time?</t>
+          <t>Customer Phone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>select_service_frequency</t>
+          <t>customer_address</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How often would you like to get service?</t>
+          <t>Customer Address</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>select_service_day</t>
+          <t>customer_inquiry</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Which day of the week?</t>
+          <t>Inquiry Description</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>select_service_time_frame</t>
+          <t>customer_message</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Time Frame</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>custom_select_service_provider_2</t>
+          <t>select_service_provider_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Select Service Provider 2</t>
+          <t>Additional Service Provider</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,251 +860,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>select_service_provider_3</t>
+          <t>custom_tailoring_inquiry_contact_form_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Select Service Provider 3</t>
+          <t>Custom Tailoring Inquiry Contact Form 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>custom_select_service_provider_4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Select Service Provider 4</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>select_service_provider_5</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Select Service Provider 5</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>custom_tailoring_inquiry_contact_form_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Custom Tailoring Inquiry Contact Form 2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>select_service_type_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What is the type of tailoring service?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>select_service_location_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Which location do you want to receive service at?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>select_service_time_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is the preferred service time?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>select_service_frequency_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How often would you like to get service?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>select_service_day_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Which day of the week?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>select_service_time_frame_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Time Frame</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>select_service_provider_2_2</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Select Service Provider 2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1121,10 +891,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1149,51 +919,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_inquiry_type_choices</t>
+          <t>select_tailoring_service_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sewing</t>
+          <t>alterations</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sewing</t>
+          <t>Alterations</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_inquiry_type_choices</t>
+          <t>select_tailoring_service_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>alterations</t>
+          <t>repairs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alterations</t>
+          <t>Repairs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_inquiry_type_choices</t>
+          <t>select_service_location_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>repairs</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1205,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>work</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Work</t>
         </is>
       </c>
     </row>
@@ -1222,29 +992,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>work</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_service_location_choices</t>
+          <t>select_service_time_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>9am_-_5pm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>9am - 5pm</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9am_-_5pm</t>
+          <t>after_5pm_-_10pm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9am - 5pm</t>
+          <t>After 5pm - 10pm</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>after_5pm_-_10pm</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>After 5pm - 10pm</t>
+          <t>Weekend</t>
         </is>
       </c>
     </row>
@@ -1290,29 +1060,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>weekend</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_service_time_choices</t>
+          <t>select_service_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1358,29 +1128,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bi-weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bi-Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_service_frequency_choices</t>
+          <t>select_service_day_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>monday</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>tuesday</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>wednesday</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>thursday</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>friday</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1477,29 +1247,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>saturday</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_service_day_choices</t>
+          <t>select_service_time_frame_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sunday</t>
+          <t>9am_-_1pm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>9am - 1pm</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1281,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9am_-_1pm</t>
+          <t>1pm_-_3pm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9am - 1pm</t>
+          <t>1pm - 3pm</t>
         </is>
       </c>
     </row>
@@ -1528,29 +1298,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1pm_-_3pm</t>
+          <t>3pm_-_5pm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1pm - 3pm</t>
+          <t>3pm - 5pm</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_service_time_frame_choices</t>
+          <t>select_service_provider_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3pm_-_5pm</t>
+          <t>alterations</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3pm - 5pm</t>
+          <t>Alterations</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1332,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>alterations</t>
+          <t>sewing</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alterations</t>
+          <t>Sewing</t>
         </is>
       </c>
     </row>
@@ -1579,707 +1349,61 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sewing</t>
+          <t>repair</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sewing</t>
+          <t>Repair</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_service_provider_choices</t>
+          <t>select_service_provider_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>repair</t>
+          <t>alterations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Repair</t>
+          <t>Alterations</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>custom_select_service_provider_2_choices</t>
+          <t>select_service_provider_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>alterations</t>
+          <t>sewing</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alterations</t>
+          <t>Sewing</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>custom_select_service_provider_2_choices</t>
+          <t>select_service_provider_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sewing</t>
+          <t>repair</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
-        <is>
-          <t>Sewing</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>custom_select_service_provider_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>repair</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Repair</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>select_service_provider_3_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>alterations</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Alterations</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>select_service_provider_3_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>sewing</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Sewing</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>select_service_provider_3_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>repair</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Repair</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>custom_select_service_provider_4_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>alterations</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Alterations</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>custom_select_service_provider_4_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>sewing</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Sewing</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>custom_select_service_provider_4_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>repair</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Repair</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>select_service_provider_5_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>alterations</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Alterations</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>select_service_provider_5_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>sewing</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Sewing</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>select_service_provider_5_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>repair</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Repair</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>custom_tailoring_inquiry_contact_form_2_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>alterations</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Alterations</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>custom_tailoring_inquiry_contact_form_2_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>repair</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Repair</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>select_service_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>alterations</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Alterations</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>select_service_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>repairs</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>select_service_location_2_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>select_service_location_2_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>work</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Work</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>select_service_location_2_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>office</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>select_service_time_2_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>9am_-_5pm</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>9am - 5pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>select_service_time_2_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>after_5pm_-_10pm</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>After 5pm - 10pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>select_service_time_2_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Weekend</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>select_service_time_2_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>select_service_frequency_2_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>select_service_frequency_2_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>select_service_frequency_2_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>bi-weekly</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Bi-Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>select_service_frequency_2_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>select_service_day_2_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>monday</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>select_service_day_2_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>tuesday</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>select_service_day_2_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>wednesday</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>select_service_day_2_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>thursday</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>select_service_day_2_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>friday</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>select_service_day_2_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>saturday</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>select_service_day_2_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>sunday</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>select_service_time_frame_2_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>9am_-_1pm</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>9am - 1pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>select_service_time_frame_2_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>1pm_-_3pm</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1pm - 3pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>select_service_time_frame_2_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>3pm_-_5pm</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>3pm - 5pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>select_service_provider_2_2_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>alterations</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Alterations</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>select_service_provider_2_2_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>sewing</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Sewing</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>select_service_provider_2_2_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>repair</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
         <is>
           <t>Repair</t>
         </is>
